--- a/public/templates/01_도서부_봉사시간_누적관리/도서부_봉사시간_누적관리.xlsx
+++ b/public/templates/01_도서부_봉사시간_누적관리/도서부_봉사시간_누적관리.xlsx
@@ -1222,17 +1222,45 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="A4" s="12" t="n">
+        <v>10102</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>이예시</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>010-0000-0002</t>
+        </is>
+      </c>
       <c r="E4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="A5" s="12" t="n">
+        <v>10203</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>박예시</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>010-0000-0003</t>
+        </is>
+      </c>
       <c r="E5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1863,199 +1891,311 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="16" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>10101</v>
+      </c>
       <c r="C3" s="17" t="str">
         <f aca="false">IF($B3="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B3,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19" t="str">
+        <v>학번없음</v>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>일상봉사</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G3" s="19" t="n">
         <f aca="false">IF(OR($E3="",$F3=""),"",ROUND(IF($F3&lt;1,$F3*24,INT($F3/100)+MOD($F3,100)/60)-IF($E3&lt;1,$E3*24,INT($E3/100)+MOD($E3,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="17" t="str">
+        <v>0.83</v>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>도서 대출·반납 도우미</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="n">
         <f aca="false">IF($A3="","",YEAR($A3))</f>
-        <v/>
-      </c>
-      <c r="J3" s="17" t="str">
+        <v>2026</v>
+      </c>
+      <c r="J3" s="17" t="n">
         <f aca="false">IF($A3="","",MONTH($A3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K3" s="17" t="str">
         <f aca="false">IF($A3="","",IF(AND($A3&gt;=사용안내!$C$18,$A3&lt;=사용안내!$C$19),"1학기",IF(AND($A3&gt;=사용안내!$C$20,$A3&lt;=사용안내!$C$21),"2학기","기간외")))</f>
-        <v/>
+        <v>1학기</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="16" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>10102</v>
+      </c>
       <c r="C4" s="17" t="str">
         <f aca="false">IF($B4="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B4,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19" t="str">
+        <v>이예시</v>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>일상봉사</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G4" s="19" t="n">
         <f aca="false">IF(OR($E4="",$F4=""),"",ROUND(IF($F4&lt;1,$F4*24,INT($F4/100)+MOD($F4,100)/60)-IF($E4&lt;1,$E4*24,INT($E4/100)+MOD($E4,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="17" t="str">
+        <v>0.83</v>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>서가 정리</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="n">
         <f aca="false">IF($A4="","",YEAR($A4))</f>
-        <v/>
-      </c>
-      <c r="J4" s="17" t="str">
+        <v>2026</v>
+      </c>
+      <c r="J4" s="17" t="n">
         <f aca="false">IF($A4="","",MONTH($A4))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K4" s="17" t="str">
         <f aca="false">IF($A4="","",IF(AND($A4&gt;=사용안내!$C$18,$A4&lt;=사용안내!$C$19),"1학기",IF(AND($A4&gt;=사용안내!$C$20,$A4&lt;=사용안내!$C$21),"2학기","기간외")))</f>
-        <v/>
+        <v>1학기</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="16" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>10101</v>
+      </c>
       <c r="C5" s="17" t="str">
         <f aca="false">IF($B5="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B5,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19" t="str">
+        <v>학번없음</v>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>특별봉사</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G5" s="19" t="n">
         <f aca="false">IF(OR($E5="",$F5=""),"",ROUND(IF($F5&lt;1,$F5*24,INT($F5/100)+MOD($F5,100)/60)-IF($E5&lt;1,$E5*24,INT($E5/100)+MOD($E5,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="17" t="str">
+        <v>3</v>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>독서의 달 행사 준비</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="n">
         <f aca="false">IF($A5="","",YEAR($A5))</f>
-        <v/>
-      </c>
-      <c r="J5" s="17" t="str">
+        <v>2026</v>
+      </c>
+      <c r="J5" s="17" t="n">
         <f aca="false">IF($A5="","",MONTH($A5))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K5" s="17" t="str">
         <f aca="false">IF($A5="","",IF(AND($A5&gt;=사용안내!$C$18,$A5&lt;=사용안내!$C$19),"1학기",IF(AND($A5&gt;=사용안내!$C$20,$A5&lt;=사용안내!$C$21),"2학기","기간외")))</f>
-        <v/>
+        <v>1학기</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="16" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>10203</v>
+      </c>
       <c r="C6" s="17" t="str">
         <f aca="false">IF($B6="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B6,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19" t="str">
+        <v>박예시</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>일상봉사</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G6" s="19" t="n">
         <f aca="false">IF(OR($E6="",$F6=""),"",ROUND(IF($F6&lt;1,$F6*24,INT($F6/100)+MOD($F6,100)/60)-IF($E6&lt;1,$E6*24,INT($E6/100)+MOD($E6,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="17" t="str">
+        <v>0.83</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>도서 대출·반납 도우미</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="n">
         <f aca="false">IF($A6="","",YEAR($A6))</f>
-        <v/>
-      </c>
-      <c r="J6" s="17" t="str">
+        <v>2026</v>
+      </c>
+      <c r="J6" s="17" t="n">
         <f aca="false">IF($A6="","",MONTH($A6))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K6" s="17" t="str">
         <f aca="false">IF($A6="","",IF(AND($A6&gt;=사용안내!$C$18,$A6&lt;=사용안내!$C$19),"1학기",IF(AND($A6&gt;=사용안내!$C$20,$A6&lt;=사용안내!$C$21),"2학기","기간외")))</f>
-        <v/>
+        <v>1학기</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>10101</v>
+      </c>
       <c r="C7" s="17" t="str">
         <f aca="false">IF($B7="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B7,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19" t="str">
+        <v>학번없음</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>일상봉사</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G7" s="19" t="n">
         <f aca="false">IF(OR($E7="",$F7=""),"",ROUND(IF($F7&lt;1,$F7*24,INT($F7/100)+MOD($F7,100)/60)-IF($E7&lt;1,$E7*24,INT($E7/100)+MOD($E7,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="17" t="str">
+        <v>0.83</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>신간 도서 등록</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="n">
         <f aca="false">IF($A7="","",YEAR($A7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="17" t="str">
+        <v>2026</v>
+      </c>
+      <c r="J7" s="17" t="n">
         <f aca="false">IF($A7="","",MONTH($A7))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="K7" s="17" t="str">
         <f aca="false">IF($A7="","",IF(AND($A7&gt;=사용안내!$C$18,$A7&lt;=사용안내!$C$19),"1학기",IF(AND($A7&gt;=사용안내!$C$20,$A7&lt;=사용안내!$C$21),"2학기","기간외")))</f>
-        <v/>
+        <v>2학기</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16"/>
-      <c r="B8" s="12"/>
+      <c r="A8" s="16" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>10102</v>
+      </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IF($B8="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B8,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19" t="str">
+        <v>이예시</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>특별봉사</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1630</v>
+      </c>
+      <c r="G8" s="19" t="n">
         <f aca="false">IF(OR($E8="",$F8=""),"",ROUND(IF($F8&lt;1,$F8*24,INT($F8/100)+MOD($F8,100)/60)-IF($E8&lt;1,$E8*24,INT($E8/100)+MOD($E8,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="17" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>도서관 대청소</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="n">
         <f aca="false">IF($A8="","",YEAR($A8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="17" t="str">
+        <v>2026</v>
+      </c>
+      <c r="J8" s="17" t="n">
         <f aca="false">IF($A8="","",MONTH($A8))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="K8" s="17" t="str">
         <f aca="false">IF($A8="","",IF(AND($A8&gt;=사용안내!$C$18,$A8&lt;=사용안내!$C$19),"1학기",IF(AND($A8&gt;=사용안내!$C$20,$A8&lt;=사용안내!$C$21),"2학기","기간외")))</f>
-        <v/>
+        <v>2학기</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="16" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>10203</v>
+      </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IF($B9="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B9,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19" t="str">
+        <v>박예시</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>일상봉사</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G9" s="19" t="n">
         <f aca="false">IF(OR($E9="",$F9=""),"",ROUND(IF($F9&lt;1,$F9*24,INT($F9/100)+MOD($F9,100)/60)-IF($E9&lt;1,$E9*24,INT($E9/100)+MOD($E9,100)/60),2))</f>
-        <v/>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="17" t="str">
+        <v>0.83</v>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>도서 대출·반납 도우미</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="n">
         <f aca="false">IF($A9="","",YEAR($A9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="17" t="str">
+        <v>2026</v>
+      </c>
+      <c r="J9" s="17" t="n">
         <f aca="false">IF($A9="","",MONTH($A9))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="K9" s="17" t="str">
         <f aca="false">IF($A9="","",IF(AND($A9&gt;=사용안내!$C$18,$A9&lt;=사용안내!$C$19),"1학기",IF(AND($A9&gt;=사용안내!$C$20,$A9&lt;=사용안내!$C$21),"2학기","기간외")))</f>
-        <v/>
+        <v>2학기</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15926,33 +16066,61 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="16" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>10101</v>
+      </c>
       <c r="C3" s="17" t="str">
         <f aca="false">IF($B3="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B3,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+        <v>학번없음</v>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>독서토론반</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>← 예시 행입니다. 지우고 쓰세요.</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="16" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>10102</v>
+      </c>
       <c r="C4" s="17" t="str">
         <f aca="false">IF($B4="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B4,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D4" s="12"/>
+        <v>이예시</v>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>사서 도우미 교육</t>
+        </is>
+      </c>
       <c r="E4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="16" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>10203</v>
+      </c>
       <c r="C5" s="17" t="str">
         <f aca="false">IF($B5="","",IFERROR(INDEX(학생명부!$B$3:$B$83,MATCH($B5,학생명부!$A$3:$A$83,0)),"학번없음"))</f>
-        <v/>
-      </c>
-      <c r="D5" s="12"/>
+        <v>박예시</v>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>독서토론반</t>
+        </is>
+      </c>
       <c r="E5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19017,15 +19185,15 @@
       </c>
       <c r="D3" s="19" t="n">
         <f aca="false">IF($A3="","",ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$B$3:$B$502,$A3,봉사기록!$D$3:$D$502,"일상봉사"),2))</f>
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E3" s="19" t="n">
         <f aca="false">IF($A3="","",ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$B$3:$B$502,$A3,봉사기록!$D$3:$D$502,"특별봉사"),2))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="19" t="n">
         <f aca="false">IF($A3="","",ROUND($D3+$E3,2))</f>
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="G3" s="19" t="n">
         <f aca="false">IF($A3="","",사용안내!$C$17)</f>
@@ -19033,99 +19201,99 @@
       </c>
       <c r="H3" s="19" t="n">
         <f aca="false">IF($A3="","",MAX(0,$G3-$F3))</f>
-        <v>20</v>
+        <v>15.34</v>
       </c>
       <c r="I3" s="20" t="n">
         <f aca="false">IF($A3="","",IF($G3=0,"",MIN(1,$F3/$G3)))</f>
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="J3" s="17" t="n">
         <f aca="false">IF($A3="","",COUNTIFS(독서활동기록!$B$3:$B$302,$A3))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="str">
+      <c r="A4" s="17" t="n">
         <f aca="false">IF(학생명부!$A4="","",학생명부!$A4)</f>
-        <v/>
+        <v>10102</v>
       </c>
       <c r="B4" s="17" t="str">
         <f aca="false">IF(학생명부!$A4="","",학생명부!$B4)</f>
-        <v/>
+        <v>이예시</v>
       </c>
       <c r="C4" s="17" t="str">
         <f aca="false">IF(학생명부!$A4="","",학생명부!$C4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="19" t="str">
+        <v>1-3</v>
+      </c>
+      <c r="D4" s="19" t="n">
         <f aca="false">IF($A4="","",ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$B$3:$B$502,$A4,봉사기록!$D$3:$D$502,"일상봉사"),2))</f>
-        <v/>
-      </c>
-      <c r="E4" s="19" t="str">
+        <v>0.83</v>
+      </c>
+      <c r="E4" s="19" t="n">
         <f aca="false">IF($A4="","",ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$B$3:$B$502,$A4,봉사기록!$D$3:$D$502,"특별봉사"),2))</f>
-        <v/>
-      </c>
-      <c r="F4" s="19" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F4" s="19" t="n">
         <f aca="false">IF($A4="","",ROUND($D4+$E4,2))</f>
-        <v/>
-      </c>
-      <c r="G4" s="19" t="str">
+        <v>3.33</v>
+      </c>
+      <c r="G4" s="19" t="n">
         <f aca="false">IF($A4="","",사용안내!$C$17)</f>
-        <v/>
-      </c>
-      <c r="H4" s="19" t="str">
+        <v>20</v>
+      </c>
+      <c r="H4" s="19" t="n">
         <f aca="false">IF($A4="","",MAX(0,$G4-$F4))</f>
-        <v/>
-      </c>
-      <c r="I4" s="20" t="str">
+        <v>16.67</v>
+      </c>
+      <c r="I4" s="20" t="n">
         <f aca="false">IF($A4="","",IF($G4=0,"",MIN(1,$F4/$G4)))</f>
-        <v/>
-      </c>
-      <c r="J4" s="17" t="str">
+        <v>0.1665</v>
+      </c>
+      <c r="J4" s="17" t="n">
         <f aca="false">IF($A4="","",COUNTIFS(독서활동기록!$B$3:$B$302,$A4))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="str">
+      <c r="A5" s="17" t="n">
         <f aca="false">IF(학생명부!$A5="","",학생명부!$A5)</f>
-        <v/>
+        <v>10203</v>
       </c>
       <c r="B5" s="17" t="str">
         <f aca="false">IF(학생명부!$A5="","",학생명부!$B5)</f>
-        <v/>
+        <v>박예시</v>
       </c>
       <c r="C5" s="17" t="str">
         <f aca="false">IF(학생명부!$A5="","",학생명부!$C5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="19" t="str">
+        <v>2-1</v>
+      </c>
+      <c r="D5" s="19" t="n">
         <f aca="false">IF($A5="","",ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$B$3:$B$502,$A5,봉사기록!$D$3:$D$502,"일상봉사"),2))</f>
-        <v/>
-      </c>
-      <c r="E5" s="19" t="str">
+        <v>1.66</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <f aca="false">IF($A5="","",ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$B$3:$B$502,$A5,봉사기록!$D$3:$D$502,"특별봉사"),2))</f>
-        <v/>
-      </c>
-      <c r="F5" s="19" t="str">
+        <v>0</v>
+      </c>
+      <c r="F5" s="19" t="n">
         <f aca="false">IF($A5="","",ROUND($D5+$E5,2))</f>
-        <v/>
-      </c>
-      <c r="G5" s="19" t="str">
+        <v>1.66</v>
+      </c>
+      <c r="G5" s="19" t="n">
         <f aca="false">IF($A5="","",사용안내!$C$17)</f>
-        <v/>
-      </c>
-      <c r="H5" s="19" t="str">
+        <v>20</v>
+      </c>
+      <c r="H5" s="19" t="n">
         <f aca="false">IF($A5="","",MAX(0,$G5-$F5))</f>
-        <v/>
-      </c>
-      <c r="I5" s="20" t="str">
+        <v>18.34</v>
+      </c>
+      <c r="I5" s="20" t="n">
         <f aca="false">IF($A5="","",IF($G5=0,"",MIN(1,$F5/$G5)))</f>
-        <v/>
-      </c>
-      <c r="J5" s="17" t="str">
+        <v>0.083</v>
+      </c>
+      <c r="J5" s="17" t="n">
         <f aca="false">IF($A5="","",COUNTIFS(독서활동기록!$B$3:$B$302,$A5))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22410,19 +22578,19 @@
       </c>
       <c r="D85" s="22" t="n">
         <f aca="false">ROUND(SUM(D3:D83),2)</f>
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="E85" s="22" t="n">
         <f aca="false">ROUND(SUM(E3:E83),2)</f>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="F85" s="22" t="n">
         <f aca="false">ROUND(SUM(F3:F83),2)</f>
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="J85" s="21" t="n">
         <f aca="false">SUM(J3:J83)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -22579,7 +22747,7 @@
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A10,봉사기록!$D$3:$D$502,"일상봉사"),2)</f>
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A10,봉사기록!$D$3:$D$502,"특별봉사"),2)</f>
@@ -22587,11 +22755,11 @@
       </c>
       <c r="D10" s="25" t="n">
         <f aca="false">ROUND($B10+$C10,2)</f>
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E10" s="24" t="n">
         <f aca="false">COUNTIFS(봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A10)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22600,19 +22768,19 @@
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A11,봉사기록!$D$3:$D$502,"일상봉사"),2)</f>
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="C11" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A11,봉사기록!$D$3:$D$502,"특별봉사"),2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" s="25" t="n">
         <f aca="false">ROUND($B11+$C11,2)</f>
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="E11" s="24" t="n">
         <f aca="false">COUNTIFS(봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A11)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22663,19 +22831,19 @@
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A14,봉사기록!$D$3:$D$502,"일상봉사"),2)</f>
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="C14" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A14,봉사기록!$D$3:$D$502,"특별봉사"),2)</f>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="25" t="n">
         <f aca="false">ROUND($B14+$C14,2)</f>
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="E14" s="24" t="n">
         <f aca="false">COUNTIFS(봉사기록!$I$3:$I$502,$B$3,봉사기록!$J$3:$J$502,$A14)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22747,19 +22915,19 @@
       </c>
       <c r="B18" s="27" t="n">
         <f aca="false">ROUND(SUM(B6:B17),2)</f>
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="C18" s="27" t="n">
         <f aca="false">ROUND(SUM(C6:C17),2)</f>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="D18" s="27" t="n">
         <f aca="false">ROUND(SUM(D6:D17),2)</f>
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="E18" s="26" t="n">
         <f aca="false">SUM(E6:E17)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -22825,23 +22993,23 @@
       </c>
       <c r="B4" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$K$3:$K$502,$A4,봉사기록!$D$3:$D$502,"일상봉사"),2)</f>
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="C4" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$K$3:$K$502,$A4,봉사기록!$D$3:$D$502,"특별봉사"),2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="25" t="n">
         <f aca="false">ROUND($B4+$C4,2)</f>
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="E4" s="24" t="n">
         <f aca="false">COUNTIFS(봉사기록!$K$3:$K$502,$A4)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4" s="24" t="n">
         <f aca="false">SUMPRODUCT((학생명부!$A$3:$A$83&lt;&gt;"")*(COUNTIFS(봉사기록!$B$3:$B$502,학생명부!$A$3:$A$83,봉사기록!$K$3:$K$502,$A4)&gt;0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22850,23 +23018,23 @@
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$K$3:$K$502,$A5,봉사기록!$D$3:$D$502,"일상봉사"),2)</f>
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="C5" s="25" t="n">
         <f aca="false">ROUND(SUMIFS(봉사기록!$G$3:$G$502,봉사기록!$K$3:$K$502,$A5,봉사기록!$D$3:$D$502,"특별봉사"),2)</f>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="25" t="n">
         <f aca="false">ROUND($B5+$C5,2)</f>
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="E5" s="24" t="n">
         <f aca="false">COUNTIFS(봉사기록!$K$3:$K$502,$A5)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="24" t="n">
         <f aca="false">SUMPRODUCT((학생명부!$A$3:$A$83&lt;&gt;"")*(COUNTIFS(봉사기록!$B$3:$B$502,학생명부!$A$3:$A$83,봉사기록!$K$3:$K$502,$A5)&gt;0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22900,23 +23068,23 @@
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">ROUND(SUM(B4:B6),2)</f>
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">ROUND(SUM(C4:C6),2)</f>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">ROUND(SUM(D4:D6),2)</f>
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="E7" s="26" t="n">
         <f aca="false">SUM(E4:E6)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F7" s="3" t="n">
         <f aca="false">SUMPRODUCT((학생명부!$A$3:$A$83&lt;&gt;"")*(COUNTIFS(봉사기록!$B$3:$B$502,학생명부!$A$3:$A$83)&gt;0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
